--- a/for_test/rezult2/D00755908700400000Y/specification.xlsx
+++ b/for_test/rezult2/D00755908700400000Y/specification.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,66 +446,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>POS.</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CODE</t>
+          <t>00755908700400000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>QTY.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>REMARK</t>
-        </is>
-      </c>
+          <t>Pulley assy.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00755908700400000</t>
+          <t>00755908700401010</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pulley assy.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>•Pulley</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>00755908700401010</t>
+          <t>1040100036</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>•Pulley</t>
+          <t>•Screw</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -513,22 +509,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1040100036</t>
+          <t>00755908700401020</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>•Screw</t>
+          <t>•Cover</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -536,17 +532,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>00755908700401020</t>
+          <t>1050200010</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>•Cover</t>
+          <t>•Deep grooved ball bearing</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -559,209 +555,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1050200010</t>
+          <t>204110014</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>•Deep grooved ball bearing</t>
+          <t>•Lithium-based Grease</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>204110014</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>•Lithium-based Grease</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>POS.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>QTY.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>REMARK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>00755908700400000</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pulley assy.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>00755908700401010</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>•Pulley</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1040100036</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>•Screw</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>00755908700401020</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>•Cover</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1050200010</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>•Deep grooved ball bearing</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>204110014</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>•Lithium-based Grease</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>E</t>
         </is>
